--- a/Testcase/TutorialsNinja Web Application - Test Cases (Complete and Final).xlsx
+++ b/Testcase/TutorialsNinja Web Application - Test Cases (Complete and Final).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VAA\TESTER\Selenium Test\AutomationSeleniumJavaProject\Testcase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB4768E-9A4C-4A07-875D-E3374F381AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC7C248-5BDF-4FA1-ACAE-402AE26BE02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="914" firstSheet="17" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="914" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vesion History" sheetId="2" r:id="rId1"/>
@@ -23541,7 +23541,7 @@
       <c r="G22" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="H22" s="6"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="6"/>
       <c r="J22" s="33"/>
       <c r="K22" s="6"/>

--- a/Testcase/TutorialsNinja Web Application - Test Cases (Complete and Final).xlsx
+++ b/Testcase/TutorialsNinja Web Application - Test Cases (Complete and Final).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VAA\TESTER\Selenium Test\AutomationSeleniumJavaProject\Testcase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC7C248-5BDF-4FA1-ACAE-402AE26BE02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DB3422-DEB6-4028-A278-74424081C8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="914" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="914" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vesion History" sheetId="2" r:id="rId1"/>
@@ -8175,7 +8175,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8209,6 +8209,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -8382,7 +8388,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -8490,6 +8496,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -8505,9 +8514,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9684,7 +9704,7 @@
       </c>
     </row>
     <row r="9" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H9" s="41" t="s">
+      <c r="H9" s="42" t="s">
         <v>7</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -9693,7 +9713,7 @@
       <c r="J9" s="1"/>
     </row>
     <row r="10" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H10" s="42"/>
+      <c r="H10" s="43"/>
       <c r="I10" s="1" t="s">
         <v>19</v>
       </c>
@@ -9702,7 +9722,7 @@
       </c>
     </row>
     <row r="11" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H11" s="42"/>
+      <c r="H11" s="43"/>
       <c r="I11" s="1" t="s">
         <v>21</v>
       </c>
@@ -9711,12 +9731,12 @@
       </c>
     </row>
     <row r="12" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H12" s="42"/>
+      <c r="H12" s="43"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
     <row r="13" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H13" s="43"/>
+      <c r="H13" s="44"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
@@ -9783,10 +9803,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -10126,10 +10146,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -10739,10 +10759,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -11730,10 +11750,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -12101,10 +12121,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -12742,10 +12762,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -13086,10 +13106,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -13538,10 +13558,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -13990,10 +14010,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -14658,10 +14678,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -15044,55 +15064,55 @@
       <c r="A2" s="19" t="s">
         <v>2077</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="46" t="s">
         <v>2078</v>
       </c>
-      <c r="C2" s="44"/>
+      <c r="C2" s="45"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>2079</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="46" t="s">
         <v>2080</v>
       </c>
-      <c r="C3" s="44"/>
+      <c r="C3" s="45"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
         <v>2081</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="45" t="s">
         <v>2082</v>
       </c>
-      <c r="C4" s="44"/>
+      <c r="C4" s="45"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
         <v>2083</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="44"/>
+      <c r="C5" s="45"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
         <v>2084</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="45" t="s">
         <v>2085</v>
       </c>
-      <c r="C6" s="44"/>
+      <c r="C6" s="45"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>2086</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="45" t="s">
         <v>2087</v>
       </c>
-      <c r="C7" s="44"/>
+      <c r="C7" s="45"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
@@ -15740,10 +15760,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -16056,10 +16076,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -16453,10 +16473,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -16904,10 +16924,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -17274,10 +17294,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -17833,10 +17853,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -18230,10 +18250,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -18573,10 +18593,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -19456,10 +19476,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -19907,10 +19927,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -20359,10 +20379,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -21188,10 +21208,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -21585,10 +21605,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -22117,10 +22137,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -22811,10 +22831,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -22992,10 +23012,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -23713,10 +23733,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -24110,10 +24130,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -24885,10 +24905,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -25579,10 +25599,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -26330,10 +26350,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>2131</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
@@ -26884,32 +26904,32 @@
       <c r="J22" s="33"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:11" s="52" customFormat="1" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="A23" s="47" t="s">
         <v>649</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="48" t="s">
         <v>567</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="49" t="s">
         <v>650</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="49" t="s">
         <v>241</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="49" t="s">
         <v>651</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="48" t="s">
         <v>383</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="49" t="s">
         <v>652</v>
       </c>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="6"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="50"/>
     </row>
     <row r="24" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
